--- a/excel/Kommune_HR_Lonn_Vikar_Monitor_2026.xlsx
+++ b/excel/Kommune_HR_Lonn_Vikar_Monitor_2026.xlsx
@@ -722,7 +722,7 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>SHA-256: 5d0058defa445ec42354f7e98676080cb250089e1ca75cac1882d79c113a6874</t>
+          <t>SHA-256: 72678e8e4278a7f35e05606502bec16c9fb0b1096c0ae809efcad505ecd6df7d</t>
         </is>
       </c>
     </row>
